--- a/Punkte.xlsx
+++ b/Punkte.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8aeaf44f51186dc5/Desktop/CG_Übung/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nesselbrand\Desktop\ComputerGraphics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_AD4DB114E441178AC67DF4034E52DF9C693EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8329AEBA-90F3-40B1-9BC0-68BDB86C9F16}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8633E0A0-85CC-4A59-9073-1370CEC1DD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32205" yWindow="2115" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -127,10 +127,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,12 +393,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -410,7 +406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -421,7 +417,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -432,7 +428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -443,7 +439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
@@ -454,7 +450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>5</v>
       </c>
@@ -465,7 +461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>6</v>
       </c>
@@ -476,37 +472,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" s="3">
         <v>8</v>
       </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>8</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>9</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C14" s="1">
         <f>SUM(C4:C13) / 100</f>
         <v>0.47499999999999998</v>

--- a/Punkte.xlsx
+++ b/Punkte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nesselbrand\Desktop\ComputerGraphics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8633E0A0-85CC-4A59-9073-1370CEC1DD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218EEE84-54DB-414F-B171-5179D1A70028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32205" yWindow="2115" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -479,7 +479,7 @@
       <c r="C10" s="3">
         <v>8</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>0</v>
       </c>
     </row>
@@ -490,7 +490,7 @@
       <c r="C11" s="3">
         <v>0</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>0</v>
       </c>
     </row>
@@ -498,7 +498,9 @@
       <c r="B12">
         <v>9</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3">
+        <v>7</v>
+      </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
@@ -511,7 +513,7 @@
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C14" s="1">
         <f>SUM(C4:C13) / 100</f>
-        <v>0.47499999999999998</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="D14" s="1">
         <f>SUM(D4:D13) / 100</f>
